--- a/data/dividends_info_20261007.xlsx
+++ b/data/dividends_info_20261007.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50.11000061035156</v>
+        <v>49.89500045776367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1796048670999379</v>
+        <v>0.1803787938155955</v>
       </c>
       <c r="J2" t="n">
         <v>159</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>59.15000152587891</v>
+        <v>59.95000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.183431922134002</v>
+        <v>1.167639684890102</v>
       </c>
       <c r="J3" t="n">
         <v>138</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.899999618530273</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I4" t="n">
-        <v>0.674157332266361</v>
+        <v>0.6818181670401711</v>
       </c>
       <c r="J4" t="n">
         <v>68</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>50.11000061035156</v>
+        <v>49.89500045776367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1796048670999379</v>
+        <v>0.1803787938155955</v>
       </c>
       <c r="J6" t="n">
         <v>68</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.015000104904175</v>
+        <v>2.025000095367432</v>
       </c>
       <c r="I7" t="n">
-        <v>3.82133975142705</v>
+        <v>3.802468956725087</v>
       </c>
       <c r="J7" t="n">
         <v>47</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>49.2400016784668</v>
+        <v>49.40000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>0.671608425522493</v>
+        <v>0.6694331777029562</v>
       </c>
       <c r="J8" t="n">
         <v>47</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.15500068664551</v>
+        <v>24.23500061035156</v>
       </c>
       <c r="I9" t="n">
-        <v>1.117780965948281</v>
+        <v>1.114091162369</v>
       </c>
       <c r="J9" t="n">
         <v>47</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25.27000045776367</v>
+        <v>24.92000007629395</v>
       </c>
       <c r="I10" t="n">
-        <v>2.334784286949765</v>
+        <v>2.367576236732274</v>
       </c>
       <c r="J10" t="n">
         <v>47</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11.52000045776367</v>
+        <v>11.42000007629395</v>
       </c>
       <c r="I11" t="n">
-        <v>1.822916594230469</v>
+        <v>1.838879147084471</v>
       </c>
       <c r="J11" t="n">
         <v>40</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7.690000057220459</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="I14" t="n">
-        <v>0.780234064415429</v>
+        <v>0.7228915496529372</v>
       </c>
       <c r="J14" t="n">
         <v>33</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.60999965667725</v>
+        <v>10.6899995803833</v>
       </c>
       <c r="I15" t="n">
-        <v>4.335532656784827</v>
+        <v>4.303087166103577</v>
       </c>
       <c r="J15" t="n">
         <v>19</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7.440000057220459</v>
+        <v>7.480000019073486</v>
       </c>
       <c r="I19" t="n">
-        <v>0.510752684243884</v>
+        <v>0.5080213890789119</v>
       </c>
       <c r="J19" t="n">
         <v>-9</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>24.15500068664551</v>
+        <v>24.23500061035156</v>
       </c>
       <c r="I20" t="n">
-        <v>1.117780965948281</v>
+        <v>1.114091162369</v>
       </c>
       <c r="J20" t="n">
         <v>-16</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>50.11000061035156</v>
+        <v>49.89500045776367</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1796048670999379</v>
+        <v>0.1803787938155955</v>
       </c>
       <c r="J22" t="n">
         <v>-16</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>94.30000305175781</v>
+        <v>94.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.41039231914978</v>
+        <v>1.407407407407408</v>
       </c>
       <c r="J23" t="n">
         <v>-16</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.119999885559082</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>4.901960875977926</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>-23</v>
@@ -3065,7 +3065,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3075,14 +3075,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3116,7 +3116,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3133,7 +3133,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3143,14 +3143,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3177,14 +3177,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3194,14 +3194,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3218,7 +3218,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3228,14 +3228,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3381,14 +3381,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3524,7 +3524,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3660,7 +3660,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3687,14 +3687,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3711,7 +3711,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3728,7 +3728,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3745,7 +3745,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3772,14 +3772,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3789,14 +3789,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3823,14 +3823,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3847,7 +3847,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3864,7 +3864,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3874,14 +3874,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3908,14 +3908,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3925,14 +3925,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3949,7 +3949,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3966,7 +3966,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3983,7 +3983,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4000,7 +4000,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4017,7 +4017,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4034,7 +4034,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4044,14 +4044,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4068,7 +4068,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4078,14 +4078,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4102,7 +4102,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4112,14 +4112,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4136,7 +4136,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4146,14 +4146,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4170,7 +4170,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4204,7 +4204,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4272,7 +4272,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4289,7 +4289,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4327,163 +4327,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DHH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Neodecortech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Svas Biosana S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>